--- a/data_lake/industry/Logistics/Logistic manager index.xlsx
+++ b/data_lake/industry/Logistics/Logistic manager index.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="10510"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="10821"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/junghunlee/Desktop/Pycharm/FinancialData/data_lake/industry/Logistics/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4BE6B978-2214-3F40-9D9A-D0CF5249E4FF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CA2EB1B7-A933-8A49-8689-AF1BBD8E815B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="18000" yWindow="780" windowWidth="18000" windowHeight="20760" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="18000" yWindow="780" windowWidth="18000" windowHeight="20760" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="LMI" sheetId="1" r:id="rId1"/>
@@ -857,6 +857,9 @@
                 <c:pt idx="118">
                   <c:v>46238</c:v>
                 </c:pt>
+                <c:pt idx="119">
+                  <c:v>46266</c:v>
+                </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
@@ -1222,6 +1225,9 @@
                 </c:pt>
                 <c:pt idx="118">
                   <c:v>68.900000000000006</c:v>
+                </c:pt>
+                <c:pt idx="119">
+                  <c:v>66.599999999999994</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -1622,6 +1628,9 @@
                 <c:pt idx="118">
                   <c:v>46238</c:v>
                 </c:pt>
+                <c:pt idx="119">
+                  <c:v>46266</c:v>
+                </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
@@ -1987,6 +1996,9 @@
                 </c:pt>
                 <c:pt idx="118">
                   <c:v>55</c:v>
+                </c:pt>
+                <c:pt idx="119">
+                  <c:v>52.8</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -2387,6 +2399,9 @@
                 <c:pt idx="118">
                   <c:v>46238</c:v>
                 </c:pt>
+                <c:pt idx="119">
+                  <c:v>46266</c:v>
+                </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
@@ -2752,6 +2767,9 @@
                 </c:pt>
                 <c:pt idx="118">
                   <c:v>77</c:v>
+                </c:pt>
+                <c:pt idx="119">
+                  <c:v>78.599999999999994</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -3152,6 +3170,9 @@
                 <c:pt idx="118">
                   <c:v>46238</c:v>
                 </c:pt>
+                <c:pt idx="119">
+                  <c:v>46266</c:v>
+                </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
@@ -3517,6 +3538,9 @@
                 </c:pt>
                 <c:pt idx="118">
                   <c:v>46.3</c:v>
+                </c:pt>
+                <c:pt idx="119">
+                  <c:v>53.5</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -3917,6 +3941,9 @@
                 <c:pt idx="118">
                   <c:v>46238</c:v>
                 </c:pt>
+                <c:pt idx="119">
+                  <c:v>46266</c:v>
+                </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
@@ -4282,6 +4309,9 @@
                 </c:pt>
                 <c:pt idx="118">
                   <c:v>66.099999999999994</c:v>
+                </c:pt>
+                <c:pt idx="119">
+                  <c:v>59.6</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -4682,6 +4712,9 @@
                 <c:pt idx="118">
                   <c:v>46238</c:v>
                 </c:pt>
+                <c:pt idx="119">
+                  <c:v>46266</c:v>
+                </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
@@ -5047,6 +5080,9 @@
                 </c:pt>
                 <c:pt idx="118">
                   <c:v>75.5</c:v>
+                </c:pt>
+                <c:pt idx="119">
+                  <c:v>75</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -5449,6 +5485,9 @@
                 <c:pt idx="118">
                   <c:v>46238</c:v>
                 </c:pt>
+                <c:pt idx="119">
+                  <c:v>46266</c:v>
+                </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
@@ -5814,6 +5853,9 @@
                 </c:pt>
                 <c:pt idx="118">
                   <c:v>28.4</c:v>
+                </c:pt>
+                <c:pt idx="119">
+                  <c:v>40</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -6216,6 +6258,9 @@
                 <c:pt idx="118">
                   <c:v>46238</c:v>
                 </c:pt>
+                <c:pt idx="119">
+                  <c:v>46266</c:v>
+                </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
@@ -6581,6 +6626,9 @@
                 </c:pt>
                 <c:pt idx="118">
                   <c:v>65</c:v>
+                </c:pt>
+                <c:pt idx="119">
+                  <c:v>70.599999999999994</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -6983,6 +7031,9 @@
                 <c:pt idx="118">
                   <c:v>46238</c:v>
                 </c:pt>
+                <c:pt idx="119">
+                  <c:v>46266</c:v>
+                </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
@@ -7348,6 +7399,9 @@
                 </c:pt>
                 <c:pt idx="118">
                   <c:v>86.9</c:v>
+                </c:pt>
+                <c:pt idx="119">
+                  <c:v>90</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -7897,6 +7951,9 @@
                 <c:pt idx="94">
                   <c:v>46238</c:v>
                 </c:pt>
+                <c:pt idx="95">
+                  <c:v>46266</c:v>
+                </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
@@ -8190,6 +8247,9 @@
                 </c:pt>
                 <c:pt idx="94">
                   <c:v>70.5</c:v>
+                </c:pt>
+                <c:pt idx="95">
+                  <c:v>69.599999999999994</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -8518,6 +8578,9 @@
                 <c:pt idx="94">
                   <c:v>46238</c:v>
                 </c:pt>
+                <c:pt idx="95">
+                  <c:v>46266</c:v>
+                </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
@@ -8811,6 +8874,9 @@
                 </c:pt>
                 <c:pt idx="94">
                   <c:v>64.400000000000006</c:v>
+                </c:pt>
+                <c:pt idx="95">
+                  <c:v>68.099999999999994</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -9139,6 +9205,9 @@
                 <c:pt idx="94">
                   <c:v>46238</c:v>
                 </c:pt>
+                <c:pt idx="95">
+                  <c:v>46266</c:v>
+                </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
@@ -9432,6 +9501,9 @@
                 </c:pt>
                 <c:pt idx="94">
                   <c:v>77.599999999999994</c:v>
+                </c:pt>
+                <c:pt idx="95">
+                  <c:v>79.599999999999994</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -9760,6 +9832,9 @@
                 <c:pt idx="94">
                   <c:v>46238</c:v>
                 </c:pt>
+                <c:pt idx="95">
+                  <c:v>46266</c:v>
+                </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
@@ -10053,6 +10128,9 @@
                 </c:pt>
                 <c:pt idx="94">
                   <c:v>49.5</c:v>
+                </c:pt>
+                <c:pt idx="95">
+                  <c:v>55.6</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -10381,6 +10459,9 @@
                 <c:pt idx="94">
                   <c:v>46238</c:v>
                 </c:pt>
+                <c:pt idx="95">
+                  <c:v>46266</c:v>
+                </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
@@ -10674,6 +10755,9 @@
                 </c:pt>
                 <c:pt idx="94">
                   <c:v>74.2</c:v>
+                </c:pt>
+                <c:pt idx="95">
+                  <c:v>70.8</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -11002,6 +11086,9 @@
                 <c:pt idx="94">
                   <c:v>46238</c:v>
                 </c:pt>
+                <c:pt idx="95">
+                  <c:v>46266</c:v>
+                </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
@@ -11295,6 +11382,9 @@
                 </c:pt>
                 <c:pt idx="94">
                   <c:v>76.3</c:v>
+                </c:pt>
+                <c:pt idx="95">
+                  <c:v>79.2</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -11625,6 +11715,9 @@
                 <c:pt idx="94">
                   <c:v>46238</c:v>
                 </c:pt>
+                <c:pt idx="95">
+                  <c:v>46266</c:v>
+                </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
@@ -11918,6 +12011,9 @@
                 </c:pt>
                 <c:pt idx="94">
                   <c:v>40.4</c:v>
+                </c:pt>
+                <c:pt idx="95">
+                  <c:v>43</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -12248,6 +12344,9 @@
                 <c:pt idx="94">
                   <c:v>46238</c:v>
                 </c:pt>
+                <c:pt idx="95">
+                  <c:v>46266</c:v>
+                </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
@@ -12541,6 +12640,9 @@
                 </c:pt>
                 <c:pt idx="94">
                   <c:v>71.8</c:v>
+                </c:pt>
+                <c:pt idx="95">
+                  <c:v>71.900000000000006</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -12871,6 +12973,9 @@
                 <c:pt idx="94">
                   <c:v>46238</c:v>
                 </c:pt>
+                <c:pt idx="95">
+                  <c:v>46266</c:v>
+                </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
@@ -13164,6 +13269,9 @@
                 </c:pt>
                 <c:pt idx="94">
                   <c:v>89.2</c:v>
+                </c:pt>
+                <c:pt idx="95">
+                  <c:v>86.1</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -14832,7 +14940,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:AE120"/>
+  <dimension ref="A1:AE121"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="9" defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="10.83203125" style="10" bestFit="1" customWidth="1"/>
@@ -20686,6 +20794,117 @@
         <v>59</v>
       </c>
     </row>
+    <row r="121" spans="1:31">
+      <c r="A121" s="10">
+        <v>46235</v>
+      </c>
+      <c r="B121" s="10">
+        <v>46266</v>
+      </c>
+      <c r="C121" s="11">
+        <v>0.33333333333333331</v>
+      </c>
+      <c r="D121" s="12" t="str">
+        <f t="shared" ref="D121" si="2">IF(
+AND(
+  B121 &gt;= IF(
+         YEAR(B121)&gt;=2007,
+         DATE(YEAR(B121),3,14)-WEEKDAY(DATE(YEAR(B121),3,14),1)+1 + TIME(2,0,0),
+         DATE(YEAR(B121),4,7)-WEEKDAY(DATE(YEAR(B121),4,7),1)+1 + TIME(2,0,0)
+       ),
+  B121 &lt;  IF(
+         YEAR(B121)&gt;=2007,
+         DATE(YEAR(B121),11,7)-WEEKDAY(DATE(YEAR(B121),11,7),1)+1 + TIME(2,0,0),
+         DATE(YEAR(B121),10,31)-WEEKDAY(DATE(YEAR(B121),10,31),1) + TIME(2,0,0)
+       )
+),
+"UTC-4",
+"UTC-5"
+)</f>
+        <v>UTC-4</v>
+      </c>
+      <c r="E121" s="13">
+        <v>66.599999999999994</v>
+      </c>
+      <c r="F121" s="14">
+        <v>52.8</v>
+      </c>
+      <c r="G121" s="14">
+        <v>78.599999999999994</v>
+      </c>
+      <c r="H121" s="14">
+        <v>53.5</v>
+      </c>
+      <c r="I121" s="14">
+        <v>59.6</v>
+      </c>
+      <c r="J121" s="14">
+        <v>75</v>
+      </c>
+      <c r="K121" s="14">
+        <v>40</v>
+      </c>
+      <c r="L121" s="14">
+        <v>70.599999999999994</v>
+      </c>
+      <c r="M121" s="14">
+        <v>90</v>
+      </c>
+      <c r="N121" s="16">
+        <v>63.9</v>
+      </c>
+      <c r="O121" s="16">
+        <v>66.900000000000006</v>
+      </c>
+      <c r="P121" s="16">
+        <v>88.8</v>
+      </c>
+      <c r="Q121" s="16">
+        <v>93.2</v>
+      </c>
+      <c r="R121" s="16">
+        <v>71.599999999999994</v>
+      </c>
+      <c r="S121" s="16">
+        <v>68.2</v>
+      </c>
+      <c r="T121" s="16">
+        <v>37.9</v>
+      </c>
+      <c r="U121" s="16">
+        <v>45.5</v>
+      </c>
+      <c r="V121" s="16">
+        <v>77.5</v>
+      </c>
+      <c r="W121" s="16">
+        <v>69</v>
+      </c>
+      <c r="X121" s="16">
+        <v>59.6</v>
+      </c>
+      <c r="Y121" s="16">
+        <v>59.5</v>
+      </c>
+      <c r="Z121" s="16">
+        <v>54.9</v>
+      </c>
+      <c r="AA121" s="16">
+        <v>50</v>
+      </c>
+      <c r="AB121" s="16">
+        <v>76.5</v>
+      </c>
+      <c r="AC121" s="16">
+        <v>83.3</v>
+      </c>
+      <c r="AD121" s="16">
+        <v>49</v>
+      </c>
+      <c r="AE121" s="16">
+        <v>61.9</v>
+      </c>
+    </row>
   </sheetData>
   <phoneticPr fontId="2" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -20695,7 +20914,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3BF85ECF-5DA2-D446-A4EF-6579CB12CAA0}">
-  <dimension ref="A1:AE96"/>
+  <dimension ref="A1:AE97"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="9" defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="10.83203125" style="10" bestFit="1" customWidth="1"/>
@@ -25523,6 +25742,117 @@
       </c>
       <c r="AE96" s="16">
         <v>66.400000000000006</v>
+      </c>
+    </row>
+    <row r="97" spans="1:31">
+      <c r="A97" s="10">
+        <v>46235</v>
+      </c>
+      <c r="B97" s="10">
+        <v>46266</v>
+      </c>
+      <c r="C97" s="11">
+        <v>0.33333333333333331</v>
+      </c>
+      <c r="D97" s="12" t="str">
+        <f t="shared" ref="D97" si="2">IF(
+AND(
+  B97 &gt;= IF(
+         YEAR(B97)&gt;=2007,
+         DATE(YEAR(B97),3,14)-WEEKDAY(DATE(YEAR(B97),3,14),1)+1 + TIME(2,0,0),
+         DATE(YEAR(B97),4,7)-WEEKDAY(DATE(YEAR(B97),4,7),1)+1 + TIME(2,0,0)
+       ),
+  B97 &lt;  IF(
+         YEAR(B97)&gt;=2007,
+         DATE(YEAR(B97),11,7)-WEEKDAY(DATE(YEAR(B97),11,7),1)+1 + TIME(2,0,0),
+         DATE(YEAR(B97),10,31)-WEEKDAY(DATE(YEAR(B97),10,31),1) + TIME(2,0,0)
+       )
+),
+"UTC-4",
+"UTC-5"
+)</f>
+        <v>UTC-4</v>
+      </c>
+      <c r="E97" s="15">
+        <v>69.599999999999994</v>
+      </c>
+      <c r="F97" s="16">
+        <v>68.099999999999994</v>
+      </c>
+      <c r="G97" s="16">
+        <v>79.599999999999994</v>
+      </c>
+      <c r="H97" s="16">
+        <v>55.6</v>
+      </c>
+      <c r="I97" s="16">
+        <v>70.8</v>
+      </c>
+      <c r="J97" s="16">
+        <v>79.2</v>
+      </c>
+      <c r="K97" s="16">
+        <v>43</v>
+      </c>
+      <c r="L97" s="16">
+        <v>71.900000000000006</v>
+      </c>
+      <c r="M97" s="16">
+        <v>86.1</v>
+      </c>
+      <c r="N97" s="16">
+        <v>69.400000000000006</v>
+      </c>
+      <c r="O97" s="16">
+        <v>66.2</v>
+      </c>
+      <c r="P97" s="16">
+        <v>88.6</v>
+      </c>
+      <c r="Q97" s="16">
+        <v>79.5</v>
+      </c>
+      <c r="R97" s="16">
+        <v>77.599999999999994</v>
+      </c>
+      <c r="S97" s="16">
+        <v>56.8</v>
+      </c>
+      <c r="T97" s="16">
+        <v>38.6</v>
+      </c>
+      <c r="U97" s="16">
+        <v>54.5</v>
+      </c>
+      <c r="V97" s="16">
+        <v>82.4</v>
+      </c>
+      <c r="W97" s="16">
+        <v>71.400000000000006</v>
+      </c>
+      <c r="X97" s="16">
+        <v>69.599999999999994</v>
+      </c>
+      <c r="Y97" s="16">
+        <v>73.8</v>
+      </c>
+      <c r="Z97" s="16">
+        <v>51</v>
+      </c>
+      <c r="AA97" s="16">
+        <v>66.7</v>
+      </c>
+      <c r="AB97" s="16">
+        <v>79</v>
+      </c>
+      <c r="AC97" s="16">
+        <v>81</v>
+      </c>
+      <c r="AD97" s="16">
+        <v>66.7</v>
+      </c>
+      <c r="AE97" s="16">
+        <v>71.400000000000006</v>
       </c>
     </row>
   </sheetData>
